--- a/data/trans_orig/IQ2608_R3-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IQ2608_R3-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>87501</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>78425</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>97466</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>53,05%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>65,93%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>111</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>74065</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>64804</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>83049</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>64481</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>83598</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>55,27%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>48,36%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>61,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>87501</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>77780</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>96210</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>59,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>148493</t>
+          <t>146865</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174694</t>
+          <t>174956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60322</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50357</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69398</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>34,07%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>46,95%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>59947</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50963</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>69208</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50414</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69531</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>44,73%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>51,64%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60322</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>51613</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>70043</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>40,81%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>37,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>107141</t>
+          <t>106879</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>133342</t>
+          <t>134970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,89%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147823</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>134012</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147823</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>129848</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>117573</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>141454</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>61,95%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>56,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>67,49%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>108604</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>97540</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>118647</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>97417</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>118942</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>56,36%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>50,62%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>61,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>196</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>129848</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>118618</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>140325</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>61,95%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>223300</t>
+          <t>223695</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>254437</t>
+          <t>254145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68147</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92028</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>38,05%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>32,51%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>43,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>84083</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>74040</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>95147</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>73745</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>95270</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>43,64%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>38,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,38%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>69276</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>90983</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>38,05%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>147851</t>
+          <t>148143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178988</t>
+          <t>178593</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,49%</t>
+          <t>44,39%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>209601</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>308</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>192687</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>209601</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,74 +1409,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90702</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>81556</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>99855</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>56,88%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>69,65%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>81566</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>72391</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>89902</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>73111</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>89909</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>61,97%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>55,55%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>68,31%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>90702</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>81943</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>100116</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>57,15%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>69,83%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>282</t>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>159371</t>
+          <t>159969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184482</t>
+          <t>183607</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>66,77%</t>
         </is>
       </c>
     </row>
@@ -1527,67 +1527,67 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>52675</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43522</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>61821</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,35%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>43,12%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>50049</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41713</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>59224</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>41706</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>58504</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,03%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>31,69%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>45,0%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>52675</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>43261</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>61434</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>30,17%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>90510</t>
+          <t>91385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115621</t>
+          <t>115023</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,83%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>143377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>143377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>143377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>131615</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>143377</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>143377</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>143377</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>141460</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>129736</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>151857</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>68,51%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>62,84%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>73,55%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>182</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>138439</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>126049</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>149070</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>127815</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>151309</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>67,09%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>61,09%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>141460</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>130141</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>151460</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>68,51%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>263110</t>
+          <t>262374</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>296210</t>
+          <t>293506</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,1%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65007</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>54610</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>76731</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>31,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>26,45%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>37,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>67910</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>57279</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>80300</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>55040</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>78534</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>38,91%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>65007</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>55007</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>76326</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>31,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116606</t>
+          <t>119310</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>149706</t>
+          <t>150442</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206467</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206349</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>304</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>206467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>676</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>449512</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>427713</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>469268</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,56%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>60,47%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>66,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>606</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>402674</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>382463</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>421897</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>383130</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>422022</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>60,58%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,54%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>63,48%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>449512</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>430161</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>470967</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,56%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>824752</t>
+          <t>821846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>881865</t>
+          <t>881029</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>60,12%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,28%</t>
+          <t>64,22%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>387</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>257756</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>238000</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>279555</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>33,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,53%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>386</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>261989</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>242766</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>282200</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>242641</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>281533</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>39,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,52%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,46%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>387</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>257756</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>236301</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>277107</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>36,44%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>490065</t>
+          <t>490901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>547178</t>
+          <t>550084</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,1%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>707268</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>992</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>664663</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>707268</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>122134</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>113282</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>129359</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,52%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,4%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>114547</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>107055</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>121197</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>106126</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>121480</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>83,01%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,58%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>87,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>122134</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>113465</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>128799</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>82,52%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>226249</t>
+          <t>225173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>246875</t>
+          <t>246023</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,02%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25874</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18649</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>34726</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,48%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>23448</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>16798</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>30940</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>16515</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>31869</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>16,99%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>12,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>22,42%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>25874</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>19209</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>34543</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>17,48%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>39981</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>59755</t>
+          <t>60831</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,27%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148008</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>137995</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148008</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>184890</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>175525</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>192950</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>80,62%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>251</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>163243</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>154471</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>170919</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>154074</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>170419</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>82,18%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>77,76%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>86,04%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>184890</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>175122</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>192690</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>84,92%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>77,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>334282</t>
+          <t>335636</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>359479</t>
+          <t>359613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,37%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32840</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>24780</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>42205</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>19,38%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>35397</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27721</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44169</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>28221</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>44566</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>17,82%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,96%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>22,24%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>32840</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>25040</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>42608</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>22,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>56891</t>
+          <t>56757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>82088</t>
+          <t>80734</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>217730</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>307</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>198640</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>315</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>217730</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>120380</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>111792</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>128483</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>75,99%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>70,57%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>81,11%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>114238</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>105463</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>121557</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>105208</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>122094</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>75,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>80,79%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>120380</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>110854</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>127635</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221793</t>
+          <t>222421</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>245778</t>
+          <t>246194</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>79,57%</t>
+          <t>79,71%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>38027</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29924</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>46615</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>24,01%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>18,89%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29,43%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>36226</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>28907</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>45001</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>28370</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>45256</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>24,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>38027</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>30772</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>47553</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63093</t>
+          <t>62677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87078</t>
+          <t>86450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,99%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158407</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>150464</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>166816</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>156354</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>174999</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>82,6%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>86,66%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>165703</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>155917</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>174935</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>155569</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>174673</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>81,78%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>76,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>86,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>166816</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>157068</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>174864</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>82,6%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>77,78%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>318637</t>
+          <t>317844</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>344771</t>
+          <t>345528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -3817,67 +3817,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>35131</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>26948</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>45593</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13,34%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>36909</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>27677</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>46695</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>27939</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>47043</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>18,22%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>23,05%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>35131</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>27083</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>44879</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>17,4%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>59031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>85922</t>
+          <t>86715</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>201947</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>265</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202612</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202612</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202612</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>274</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>201947</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>594219</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>576562</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>609777</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>81,84%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>79,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>83,98%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>557731</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>541099</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>574532</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>538893</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>573373</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>80,86%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>594219</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>575995</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>611031</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>81,84%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,33%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1126863</t>
+          <t>1127254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1176791</t>
+          <t>1176340</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>131873</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>116315</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>149530</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18,16%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>16,02%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>131980</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>115179</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>148612</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>116338</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>150818</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>19,14%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>131873</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>115061</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>150097</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>18,16%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239012</t>
+          <t>239463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>288940</t>
+          <t>288549</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1035</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>726092</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>993</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>689711</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1035</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>726092</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>131589</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>123790</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>136923</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>89,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>84,03%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>92,95%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>103416</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>94873</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>110620</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>95161</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>110633</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>78,85%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,33%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>84,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>131589</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>125159</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>137677</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>89,33%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>72,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>223563</t>
+          <t>224400</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>243790</t>
+          <t>244444</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,78%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15725</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>10391</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23524</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7,05%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,97%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27745</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20541</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36288</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>20528</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36000</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>21,15%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>15,66%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>15725</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>9637</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>22155</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>10,67%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>34030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>54911</t>
+          <t>54074</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>147314</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>131161</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>147314</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>182601</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>172872</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>191230</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>82,33%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>77,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>86,22%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>268</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>166833</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>156971</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>174449</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>157162</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>173589</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>81,47%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>76,65%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>182601</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>172858</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>190565</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>82,33%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>76,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>335335</t>
+          <t>336495</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>361053</t>
+          <t>361581</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39189</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>30560</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>48918</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>17,67%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>22,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>37956</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30340</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>47818</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31200</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>23,35%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>39189</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>31225</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>48932</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65526</t>
+          <t>64998</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>91244</t>
+          <t>90084</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,12%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>221790</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>330</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>204789</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>221790</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>142359</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>134067</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>149193</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>86,01%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>81,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>90,14%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>137791</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>131749</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>143073</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>131509</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>142988</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>90,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>93,55%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>142359</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>133600</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>148641</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>86,01%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>93,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>269923</t>
+          <t>271101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>288360</t>
+          <t>289329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,86%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>23148</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16314</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>31440</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13,99%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>15153</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>9871</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21195</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>9956</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>21435</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>9,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>13,86%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23148</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>16866</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>31907</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>13,99%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>29122</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48528</t>
+          <t>47350</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>152944</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>246</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157248</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>147947</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>166782</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>77,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>82,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>150328</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>138862</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>160317</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>139842</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>160340</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>73,46%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>67,85%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>78,34%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>157248</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>147211</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>166557</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>77,57%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>293353</t>
+          <t>292945</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>321724</t>
+          <t>321629</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>78,95%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>45473</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>35939</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>54774</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>22,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>17,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>54318</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>44329</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>65784</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>44306</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>64804</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>26,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>21,66%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>32,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>45473</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>36164</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>55510</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>22,43%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>85643</t>
+          <t>85738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>114014</t>
+          <t>114422</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>202721</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>204646</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>286</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>202721</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>613797</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>596134</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>629014</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>83,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>80,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>85,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>845</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>558368</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>541123</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>574331</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>540588</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>573493</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>80,51%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>78,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>82,81%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>878</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>613797</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>597211</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>631168</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>83,25%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>81,0%</t>
+          <t>77,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1148659</t>
+          <t>1149605</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1195316</t>
+          <t>1195652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>123535</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>108318</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>141198</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>16,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>19,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>135172</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>119209</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>152417</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>120047</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>152952</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>19,49%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>17,19%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>21,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>123535</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>106164</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>140121</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>16,75%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>235555</t>
+          <t>235219</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>282212</t>
+          <t>281266</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,66%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>737332</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1043</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>693540</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>737332</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>24813</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>19724</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28165</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>86,74%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>16844</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>12820</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20418</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>61,94%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,14%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>75,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>27198</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>22204</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30455</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>61,31%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>63,02%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44042</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>37052</t>
+          <t>35013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49197</t>
+          <t>47225</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7659</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4307</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12748</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13,26%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>39,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>10351</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6777</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14375</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>38,06%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,86%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8035</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4778</t>
+          <t>7201</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13029</t>
+          <t>14993</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>18391</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12983</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25376</t>
+          <t>25195</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,65%</t>
+          <t>41,85%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>32472</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>27195</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35233</t>
+          <t>27736</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>62428</t>
+          <t>60208</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>46798</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>40860</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>51296</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>79,6%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>69,5%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>87,25%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>29505</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24446</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>33742</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>75,05%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>62,18%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>85,83%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50338</t>
+          <t>30014</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43655</t>
+          <t>24448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55452</t>
+          <t>33875</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>79842</t>
+          <t>76813</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>71751</t>
+          <t>69377</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>86650</t>
+          <t>83577</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11994</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7496</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>17932</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>20,4%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30,5%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9809</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5572</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>14868</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24,95%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,17%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12182</t>
+          <t>9350</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7068</t>
+          <t>5489</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>14916</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21992</t>
+          <t>21343</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15184</t>
+          <t>14579</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30083</t>
+          <t>28779</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>58792</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>39314</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62520</t>
+          <t>39364</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>101834</t>
+          <t>98156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22699</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16391</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>27970</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>54,69%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>39,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,39%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>17766</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>12900</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22666</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>58,79%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>42,69%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>75,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24132</t>
+          <t>14701</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>53,89%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>68,65%</t>
+          <t>67,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>41897</t>
+          <t>37400</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34286</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50156</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>54,37%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>64,5%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>18808</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>13537</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>25116</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>45,31%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>32,61%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>60,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12455</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>7555</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>17321</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>41,21%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>25,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57,31%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>20056</t>
+          <t>12576</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13854</t>
+          <t>8812</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26270</t>
+          <t>17165</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>32512</t>
+          <t>31384</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24253</t>
+          <t>24417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>40123</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>45,63%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>56,15%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41507</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>30221</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>44188</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>74409</t>
+          <t>68784</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>27647</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>20923</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33238</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>60,64%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>45,89%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>72,9%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>29103</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>23127</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>34035</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>62,77%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>49,88%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>73,41%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30840</t>
+          <t>27386</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23995</t>
+          <t>21537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36906</t>
+          <t>32590</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>59943</t>
+          <t>55033</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51264</t>
+          <t>46511</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>68296</t>
+          <t>62304</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>51,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>17947</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12356</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>24671</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>39,36%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>27,1%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>54,11%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>17261</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12329</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>23237</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>37,23%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>26,59%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>50,12%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>18989</t>
+          <t>17771</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12923</t>
+          <t>12567</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25834</t>
+          <t>23620</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>36250</t>
+          <t>35718</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>27897</t>
+          <t>28447</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>44929</t>
+          <t>44240</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>48,75%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>45594</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>46364</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>46364</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>46364</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49829</t>
+          <t>45157</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>96193</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>96193</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>96193</t>
+          <t>90751</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>121957</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>110250</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>133410</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>61,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>74,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>146</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>93216</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>83202</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>101927</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>58,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>132508</t>
+          <t>89106</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>120350</t>
+          <t>79324</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>144765</t>
+          <t>97910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,76%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>225724</t>
+          <t>211062</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>210701</t>
+          <t>195323</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>241588</t>
+          <t>225383</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>70,9%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>56408</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44955</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>68115</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,63%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>78</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>49877</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>41166</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>59891</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,77%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59262</t>
+          <t>50428</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47005</t>
+          <t>41624</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71420</t>
+          <t>60210</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>109139</t>
+          <t>106837</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>93275</t>
+          <t>92516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124162</t>
+          <t>122576</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>178365</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>143093</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>139534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>334863</t>
+          <t>317899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
